--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251223_201456.xlsx
@@ -5032,7 +5032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
